--- a/Ejercicios/30- Ejercicio macros probar la macro.xlsx
+++ b/Ejercicios/30- Ejercicio macros probar la macro.xlsx
@@ -1,25 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nuria López Álvarez\git\ExcelPowerBI\Ejercicios\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D05E6967-01A2-4D86-BE2B-5A55F9632D39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1879DFD5-6084-47CC-AD18-3C3BAF05243A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-21720" yWindow="1830" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Hoja1" sheetId="2" r:id="rId1"/>
-    <sheet name="Datos" sheetId="1" r:id="rId2"/>
+    <sheet name="Datos" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <pivotCaches>
-    <pivotCache cacheId="2" r:id="rId3"/>
-  </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -37,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>fecha</t>
   </si>
@@ -55,9 +51,6 @@
   </si>
   <si>
     <t>Pascual</t>
-  </si>
-  <si>
-    <t>Cuenta de Pascual</t>
   </si>
 </sst>
 </file>
@@ -96,10 +89,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -115,478 +107,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" invalid="1" refreshedBy="Nuria López Álvarez" refreshedDate="46133.773951736111" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="31" xr:uid="{597C83D6-4379-47CC-B11F-E3C56EBED988}">
-  <cacheSource type="worksheet">
-    <worksheetSource ref="A1:F32" sheet="Datos"/>
-  </cacheSource>
-  <cacheFields count="6">
-    <cacheField name="fecha" numFmtId="164">
-      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2026-01-01T00:00:00" maxDate="2026-02-01T00:00:00"/>
-    </cacheField>
-    <cacheField name="Marisa" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="10"/>
-    </cacheField>
-    <cacheField name="Edelmiro" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="10"/>
-    </cacheField>
-    <cacheField name="Pascual" numFmtId="0">
-      <sharedItems containsMixedTypes="1" containsNumber="1" containsInteger="1" minValue="0" maxValue="10"/>
-    </cacheField>
-    <cacheField name="María" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="10"/>
-    </cacheField>
-    <cacheField name="Pedro" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="10"/>
-    </cacheField>
-  </cacheFields>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
-      <x14:pivotCacheDefinition/>
-    </ext>
-    <ext xmlns:xxpvi="http://schemas.microsoft.com/office/spreadsheetml/2022/pivotVersionInfo" uri="{9F748A41-CAEA-4470-BF7A-CE61E8FFA7F9}">
-      <xxpvi:cacheVersionInfo>
-        <xxpvi:lastRefreshFeature>RichData</xxpvi:lastRefreshFeature>
-      </xxpvi:cacheVersionInfo>
-    </ext>
-    <ext xmlns:xprd="http://schemas.microsoft.com/office/spreadsheetml/2022/pivotRichData" uri="{2C874A73-7782-4A18-856F-96AC7E287872}">
-      <xprd:richInfo pivotCacheGuid="{597C83D6-4379-47CC-B11F-E3C56EBED988}" pivotIgnoreInvalidCache="1" r:id="rId1"/>
-    </ext>
-  </extLst>
-</pivotCacheDefinition>
-</file>
-
-<file path=xl/pivotCache/richPivotRecords1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="31">
-  <r>
-    <d v="2026-01-01T00:00:00"/>
-    <n v="10"/>
-    <n v="6"/>
-    <n v="10"/>
-    <n v="3"/>
-    <n v="4"/>
-  </r>
-  <r>
-    <d v="2026-01-02T00:00:00"/>
-    <n v="9"/>
-    <n v="10"/>
-    <n v="3"/>
-    <n v="1"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <d v="2026-01-03T00:00:00"/>
-    <n v="5"/>
-    <n v="6"/>
-    <n v="5"/>
-    <n v="1"/>
-    <n v="2"/>
-  </r>
-  <r>
-    <d v="2026-01-04T00:00:00"/>
-    <n v="1"/>
-    <n v="2"/>
-    <n v="9"/>
-    <n v="3"/>
-    <n v="3"/>
-  </r>
-  <r>
-    <d v="2026-01-05T00:00:00"/>
-    <n v="1"/>
-    <n v="2"/>
-    <n v="6"/>
-    <n v="10"/>
-    <n v="10"/>
-  </r>
-  <r>
-    <d v="2026-01-06T00:00:00"/>
-    <n v="5"/>
-    <n v="1"/>
-    <n v="8"/>
-    <n v="2"/>
-    <n v="7"/>
-  </r>
-  <r>
-    <d v="2026-01-07T00:00:00"/>
-    <n v="9"/>
-    <n v="7"/>
-    <n v="8"/>
-    <n v="7"/>
-    <n v="5"/>
-  </r>
-  <r>
-    <d v="2026-01-08T00:00:00"/>
-    <n v="8"/>
-    <n v="4"/>
-    <n v="8"/>
-    <n v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <d v="2026-01-09T00:00:00"/>
-    <n v="10"/>
-    <n v="9"/>
-    <n v="10"/>
-    <n v="2"/>
-    <n v="8"/>
-  </r>
-  <r>
-    <d v="2026-01-10T00:00:00"/>
-    <n v="0"/>
-    <n v="0"/>
-    <s v="#CALC!"/>
-    <n v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <d v="2026-01-11T00:00:00"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <d v="2026-01-12T00:00:00"/>
-    <n v="10"/>
-    <n v="3"/>
-    <n v="9"/>
-    <n v="3"/>
-    <n v="3"/>
-  </r>
-  <r>
-    <d v="2026-01-13T00:00:00"/>
-    <n v="2"/>
-    <n v="2"/>
-    <n v="3"/>
-    <n v="0"/>
-    <n v="7"/>
-  </r>
-  <r>
-    <d v="2026-01-14T00:00:00"/>
-    <n v="4"/>
-    <n v="5"/>
-    <n v="5"/>
-    <n v="8"/>
-    <n v="2"/>
-  </r>
-  <r>
-    <d v="2026-01-15T00:00:00"/>
-    <n v="8"/>
-    <n v="8"/>
-    <n v="1"/>
-    <n v="6"/>
-    <n v="9"/>
-  </r>
-  <r>
-    <d v="2026-01-16T00:00:00"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="7"/>
-    <n v="4"/>
-    <n v="10"/>
-  </r>
-  <r>
-    <d v="2026-01-17T00:00:00"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <d v="2026-01-18T00:00:00"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <d v="2026-01-19T00:00:00"/>
-    <n v="0"/>
-    <n v="10"/>
-    <n v="1"/>
-    <n v="6"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <d v="2026-01-20T00:00:00"/>
-    <n v="10"/>
-    <n v="0"/>
-    <n v="9"/>
-    <n v="9"/>
-    <n v="7"/>
-  </r>
-  <r>
-    <d v="2026-01-21T00:00:00"/>
-    <n v="4"/>
-    <n v="8"/>
-    <n v="4"/>
-    <n v="5"/>
-    <n v="2"/>
-  </r>
-  <r>
-    <d v="2026-01-22T00:00:00"/>
-    <n v="2"/>
-    <n v="4"/>
-    <n v="4"/>
-    <n v="3"/>
-    <n v="10"/>
-  </r>
-  <r>
-    <d v="2026-01-23T00:00:00"/>
-    <n v="6"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="3"/>
-    <n v="5"/>
-  </r>
-  <r>
-    <d v="2026-01-24T00:00:00"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <d v="2026-01-25T00:00:00"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <d v="2026-01-26T00:00:00"/>
-    <n v="6"/>
-    <n v="2"/>
-    <n v="2"/>
-    <n v="10"/>
-    <n v="8"/>
-  </r>
-  <r>
-    <d v="2026-01-27T00:00:00"/>
-    <n v="1"/>
-    <n v="5"/>
-    <n v="9"/>
-    <n v="0"/>
-    <n v="7"/>
-  </r>
-  <r>
-    <d v="2026-01-28T00:00:00"/>
-    <n v="7"/>
-    <n v="2"/>
-    <n v="7"/>
-    <n v="7"/>
-    <n v="6"/>
-  </r>
-  <r>
-    <d v="2026-01-29T00:00:00"/>
-    <n v="5"/>
-    <n v="1"/>
-    <n v="8"/>
-    <n v="6"/>
-    <n v="9"/>
-  </r>
-  <r>
-    <d v="2026-01-30T00:00:00"/>
-    <n v="4"/>
-    <n v="10"/>
-    <n v="1"/>
-    <n v="9"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <d v="2026-01-31T00:00:00"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-  </r>
-</pivotCacheRecords>
-</file>
-
-<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C9EF80C4-61E3-4030-937A-D46395F8F212}" name="TablaDinámica1" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A3:A4" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
-  <pivotFields count="6">
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowItems count="1">
-    <i/>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Cuenta de Pascual" fld="3" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-    <ext xmlns:xxpvi="http://schemas.microsoft.com/office/spreadsheetml/2022/pivotVersionInfo" uri="{9F748A41-CAEA-4470-BF7A-CE61E8FFA7F9}">
-      <xxpvi:pivotVersionInfo>
-        <xxpvi:lastUpdateFeature>RichData</xxpvi:lastUpdateFeature>
-      </xxpvi:pivotVersionInfo>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
-<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
-  <global>
-    <keyFlags>
-      <key name="_Self">
-        <flag name="ExcludeFromFile" value="1"/>
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_DisplayString">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Flags">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Format">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_SubLabel">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Attribution">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Icon">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Display">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_CanonicalPropertyNames">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_ClassificationId">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-    </keyFlags>
-  </global>
-</rvTypesInfo>
-</file>
-
-<file path=xl/richData/rdarray.xml><?xml version="1.0" encoding="utf-8"?>
-<arrayData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" count="1">
-  <a r="32">
-    <v t="e">#NULL!</v>
-    <v t="e">#NULL!</v>
-    <v t="e">#NULL!</v>
-    <v t="e">#NULL!</v>
-    <v t="e">#NULL!</v>
-    <v t="e">#NULL!</v>
-    <v t="e">#NULL!</v>
-    <v t="e">#NULL!</v>
-    <v t="e">#NULL!</v>
-    <v t="r">0</v>
-    <v t="e">#NULL!</v>
-    <v t="e">#NULL!</v>
-    <v t="e">#NULL!</v>
-    <v t="e">#NULL!</v>
-    <v t="e">#NULL!</v>
-    <v t="e">#NULL!</v>
-    <v t="e">#NULL!</v>
-    <v t="e">#NULL!</v>
-    <v t="e">#NULL!</v>
-    <v t="e">#NULL!</v>
-    <v t="e">#NULL!</v>
-    <v t="e">#NULL!</v>
-    <v t="e">#NULL!</v>
-    <v t="e">#NULL!</v>
-    <v t="e">#NULL!</v>
-    <v t="e">#NULL!</v>
-    <v t="e">#NULL!</v>
-    <v t="e">#NULL!</v>
-    <v t="e">#NULL!</v>
-    <v t="e">#NULL!</v>
-    <v t="e">#NULL!</v>
-    <v t="i">2</v>
-  </a>
-</arrayData>
-</file>
-
-<file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="3">
-  <rv s="0">
-    <v>13</v>
-    <v>1</v>
-  </rv>
-  <rv s="1">
-    <v>0</v>
-  </rv>
-  <rv s="2">
-    <v>{597C83D6-4379-47CC-B11F-E3C56EBED988}</v>
-    <v>0</v>
-    <v>0</v>
-    <v>1</v>
-  </rv>
-</rvData>
-</file>
-
-<file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="3">
-  <s t="_error">
-    <k n="errorType" t="i"/>
-    <k n="propagated" t="b"/>
-  </s>
-  <s t="_array">
-    <k n="array" t="a"/>
-  </s>
-  <s t="_datasourcecontainer">
-    <k n="%XLUID" t="s"/>
-    <k n="_CRID" t="i"/>
-    <k n="_Display" t="spb"/>
-    <k n="Pascual" t="r"/>
-  </s>
-</rvStructures>
-</file>
-
-<file path=xl/richData/rdsupportingpropertybag.xml><?xml version="1.0" encoding="utf-8"?>
-<supportingPropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2">
-  <spbArrays count="1">
-    <a count="4">
-      <v t="s">Pascual</v>
-      <v t="s">_CRID</v>
-      <v t="s">%XLUID</v>
-      <v t="s">_Display</v>
-    </a>
-  </spbArrays>
-  <spbData count="1">
-    <spb s="0">
-      <v>0</v>
-    </spb>
-  </spbData>
-</supportingPropertyBags>
-</file>
-
-<file path=xl/richData/rdsupportingpropertybagstructure.xml><?xml version="1.0" encoding="utf-8"?>
-<spbStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" count="1">
-  <s>
-    <k n="^Order" t="spba"/>
-  </s>
-</spbStructures>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -873,29 +393,6 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C452D3C-12A4-4732-A56C-77A49677AC23}">
-  <dimension ref="A3:A4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="16.1796875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4" s="2">
-        <v>31</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -929,15 +426,15 @@
       </c>
       <c r="B2">
         <f t="shared" ref="B2:F7" ca="1" si="0">RANDBETWEEN(0,10)</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C2">
         <f t="shared" ca="1" si="0"/>
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D2">
         <f t="shared" ca="1" si="0"/>
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E2">
         <f t="shared" ca="1" si="0"/>
@@ -958,19 +455,19 @@
       </c>
       <c r="C3">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D3">
         <f t="shared" ca="1" si="0"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E3">
         <f t="shared" ca="1" si="0"/>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F3">
         <f t="shared" ca="1" si="0"/>
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
@@ -979,23 +476,23 @@
       </c>
       <c r="B4">
         <f t="shared" ca="1" si="0"/>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C4">
         <f t="shared" ca="1" si="0"/>
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D4">
         <f t="shared" ca="1" si="0"/>
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E4">
         <f t="shared" ca="1" si="0"/>
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F4">
         <f t="shared" ca="1" si="0"/>
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
@@ -1004,23 +501,23 @@
       </c>
       <c r="B5">
         <f t="shared" ca="1" si="0"/>
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C5">
         <f t="shared" ca="1" si="0"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D5">
         <f t="shared" ca="1" si="0"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E5">
         <f t="shared" ca="1" si="0"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F5">
         <f t="shared" ca="1" si="0"/>
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
@@ -1029,23 +526,23 @@
       </c>
       <c r="B6">
         <f t="shared" ca="1" si="0"/>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C6">
         <f t="shared" ca="1" si="0"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D6">
         <f t="shared" ca="1" si="0"/>
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E6">
         <f t="shared" ca="1" si="0"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F6">
         <f t="shared" ca="1" si="0"/>
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
@@ -1054,23 +551,23 @@
       </c>
       <c r="B7">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C7">
         <f t="shared" ca="1" si="0"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D7">
         <f t="shared" ca="1" si="0"/>
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E7">
         <f t="shared" ca="1" si="0"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F7">
         <f t="shared" ca="1" si="0"/>
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
@@ -1078,24 +575,24 @@
         <v>46029</v>
       </c>
       <c r="B8">
-        <f t="shared" ref="B2:F17" ca="1" si="1">RANDBETWEEN(0,10)</f>
-        <v>10</v>
+        <f t="shared" ref="B8:F17" ca="1" si="1">RANDBETWEEN(0,10)</f>
+        <v>0</v>
       </c>
       <c r="C8">
         <f t="shared" ca="1" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="D8">
+        <f t="shared" ca="1" si="1"/>
         <v>1</v>
       </c>
-      <c r="D8">
-        <f t="shared" ca="1" si="1"/>
-        <v>3</v>
-      </c>
       <c r="E8">
         <f t="shared" ca="1" si="1"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F8">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
@@ -1104,23 +601,23 @@
       </c>
       <c r="B9">
         <f t="shared" ca="1" si="1"/>
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C9">
         <f t="shared" ca="1" si="1"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D9">
         <f t="shared" ca="1" si="1"/>
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E9">
         <f t="shared" ca="1" si="1"/>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F9">
         <f t="shared" ca="1" si="1"/>
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
@@ -1133,19 +630,19 @@
       </c>
       <c r="C10">
         <f t="shared" ca="1" si="1"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D10">
         <f t="shared" ca="1" si="1"/>
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E10">
         <f t="shared" ca="1" si="1"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F10">
         <f t="shared" ca="1" si="1"/>
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
@@ -1154,23 +651,23 @@
       </c>
       <c r="B11">
         <f t="shared" ca="1" si="1"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C11">
         <f t="shared" ca="1" si="1"/>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D11">
         <f t="shared" ca="1" si="1"/>
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E11">
         <f t="shared" ca="1" si="1"/>
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F11">
         <f t="shared" ca="1" si="1"/>
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
@@ -1179,11 +676,11 @@
       </c>
       <c r="B12">
         <f t="shared" ca="1" si="1"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C12">
         <f t="shared" ca="1" si="1"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D12">
         <f t="shared" ca="1" si="1"/>
@@ -1191,11 +688,11 @@
       </c>
       <c r="E12">
         <f t="shared" ca="1" si="1"/>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F12">
         <f t="shared" ca="1" si="1"/>
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
@@ -1204,19 +701,19 @@
       </c>
       <c r="B13">
         <f t="shared" ca="1" si="1"/>
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C13">
         <f t="shared" ca="1" si="1"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D13">
         <f t="shared" ca="1" si="1"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E13">
         <f t="shared" ca="1" si="1"/>
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F13">
         <f t="shared" ca="1" si="1"/>
@@ -1233,19 +730,19 @@
       </c>
       <c r="C14">
         <f t="shared" ca="1" si="1"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D14">
         <f t="shared" ca="1" si="1"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E14">
         <f t="shared" ca="1" si="1"/>
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F14">
         <f t="shared" ca="1" si="1"/>
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
@@ -1254,23 +751,23 @@
       </c>
       <c r="B15">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C15">
         <f t="shared" ca="1" si="1"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D15">
         <f t="shared" ca="1" si="1"/>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E15">
         <f t="shared" ca="1" si="1"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F15">
         <f t="shared" ca="1" si="1"/>
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
@@ -1279,23 +776,23 @@
       </c>
       <c r="B16">
         <f t="shared" ca="1" si="1"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C16">
         <f t="shared" ca="1" si="1"/>
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D16">
         <f t="shared" ca="1" si="1"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E16">
         <f t="shared" ca="1" si="1"/>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F16">
         <f t="shared" ca="1" si="1"/>
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.35">
@@ -1304,15 +801,15 @@
       </c>
       <c r="B17">
         <f t="shared" ca="1" si="1"/>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C17">
         <f t="shared" ca="1" si="1"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D17">
         <f t="shared" ca="1" si="1"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E17">
         <f t="shared" ca="1" si="1"/>
@@ -1320,7 +817,7 @@
       </c>
       <c r="F17">
         <f t="shared" ca="1" si="1"/>
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.35">
@@ -1329,11 +826,11 @@
       </c>
       <c r="B18">
         <f t="shared" ref="B18:D32" ca="1" si="2">RANDBETWEEN(0,10)</f>
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C18">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D18">
         <f t="shared" ca="1" si="2"/>
@@ -1341,11 +838,11 @@
       </c>
       <c r="E18">
         <f t="shared" ref="E18:F32" ca="1" si="3">RANDBETWEEN(0,10)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F18">
         <f t="shared" ca="1" si="3"/>
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
@@ -1354,23 +851,23 @@
       </c>
       <c r="B19">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C19">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D19">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E19">
         <f t="shared" ca="1" si="3"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F19">
         <f t="shared" ca="1" si="3"/>
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
@@ -1383,19 +880,19 @@
       </c>
       <c r="C20">
         <f t="shared" ca="1" si="2"/>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D20">
         <f t="shared" ca="1" si="2"/>
+        <v>8</v>
+      </c>
+      <c r="E20">
+        <f t="shared" ca="1" si="3"/>
         <v>3</v>
       </c>
-      <c r="E20">
-        <f t="shared" ca="1" si="3"/>
-        <v>3</v>
-      </c>
       <c r="F20">
         <f t="shared" ca="1" si="3"/>
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
@@ -1404,15 +901,15 @@
       </c>
       <c r="B21">
         <f t="shared" ca="1" si="2"/>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C21">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D21">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E21">
         <f t="shared" ca="1" si="3"/>
@@ -1420,7 +917,7 @@
       </c>
       <c r="F21">
         <f t="shared" ca="1" si="3"/>
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.35">
@@ -1429,23 +926,23 @@
       </c>
       <c r="B22">
         <f t="shared" ca="1" si="2"/>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C22">
         <f t="shared" ca="1" si="2"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D22">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E22">
         <f t="shared" ca="1" si="3"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F22">
         <f t="shared" ca="1" si="3"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.35">
@@ -1454,23 +951,23 @@
       </c>
       <c r="B23">
         <f t="shared" ca="1" si="2"/>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C23">
         <f t="shared" ca="1" si="2"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D23">
         <f t="shared" ca="1" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="E23">
+        <f t="shared" ca="1" si="3"/>
+        <v>6</v>
+      </c>
+      <c r="F23">
+        <f t="shared" ca="1" si="3"/>
         <v>1</v>
-      </c>
-      <c r="E23">
-        <f t="shared" ca="1" si="3"/>
-        <v>3</v>
-      </c>
-      <c r="F23">
-        <f t="shared" ca="1" si="3"/>
-        <v>4</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.35">
@@ -1479,19 +976,19 @@
       </c>
       <c r="B24">
         <f t="shared" ca="1" si="2"/>
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C24">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D24">
         <f t="shared" ca="1" si="2"/>
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E24">
         <f t="shared" ca="1" si="3"/>
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F24">
         <f t="shared" ca="1" si="3"/>
@@ -1508,19 +1005,19 @@
       </c>
       <c r="C25">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D25">
         <f t="shared" ca="1" si="2"/>
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E25">
         <f t="shared" ca="1" si="3"/>
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F25">
         <f t="shared" ca="1" si="3"/>
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.35">
@@ -1529,23 +1026,23 @@
       </c>
       <c r="B26">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C26">
         <f t="shared" ca="1" si="2"/>
+        <v>6</v>
+      </c>
+      <c r="D26">
+        <f t="shared" ca="1" si="2"/>
         <v>1</v>
       </c>
-      <c r="D26">
-        <f t="shared" ca="1" si="2"/>
-        <v>8</v>
-      </c>
       <c r="E26">
         <f t="shared" ca="1" si="3"/>
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F26">
         <f t="shared" ca="1" si="3"/>
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.35">
@@ -1554,23 +1051,23 @@
       </c>
       <c r="B27">
         <f t="shared" ca="1" si="2"/>
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C27">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D27">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E27">
         <f t="shared" ca="1" si="3"/>
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F27">
         <f t="shared" ca="1" si="3"/>
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
@@ -1579,7 +1076,7 @@
       </c>
       <c r="B28">
         <f t="shared" ca="1" si="2"/>
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C28">
         <f t="shared" ca="1" si="2"/>
@@ -1587,15 +1084,15 @@
       </c>
       <c r="D28">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E28">
         <f t="shared" ca="1" si="3"/>
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F28">
         <f t="shared" ca="1" si="3"/>
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.35">
@@ -1604,23 +1101,23 @@
       </c>
       <c r="B29">
         <f t="shared" ca="1" si="2"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C29">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D29">
         <f t="shared" ca="1" si="2"/>
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E29">
         <f t="shared" ca="1" si="3"/>
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F29">
         <f t="shared" ca="1" si="3"/>
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
@@ -1629,23 +1126,23 @@
       </c>
       <c r="B30">
         <f t="shared" ca="1" si="2"/>
+        <v>8</v>
+      </c>
+      <c r="C30">
+        <f t="shared" ca="1" si="2"/>
         <v>1</v>
       </c>
-      <c r="C30">
-        <f t="shared" ca="1" si="2"/>
-        <v>5</v>
-      </c>
       <c r="D30">
         <f t="shared" ca="1" si="2"/>
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E30">
         <f t="shared" ca="1" si="3"/>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F30">
         <f t="shared" ca="1" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.35">
@@ -1654,11 +1151,11 @@
       </c>
       <c r="B31">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C31">
         <f t="shared" ca="1" si="2"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D31">
         <f t="shared" ca="1" si="2"/>
@@ -1666,11 +1163,11 @@
       </c>
       <c r="E31">
         <f t="shared" ca="1" si="3"/>
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F31">
         <f t="shared" ca="1" si="3"/>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.35">
@@ -1679,11 +1176,11 @@
       </c>
       <c r="B32">
         <f t="shared" ca="1" si="2"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C32">
         <f t="shared" ca="1" si="2"/>
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D32">
         <f t="shared" ca="1" si="2"/>
@@ -1691,11 +1188,11 @@
       </c>
       <c r="E32">
         <f t="shared" ca="1" si="3"/>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F32">
         <f t="shared" ca="1" si="3"/>
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
